--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_13_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_13_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2547CF-EC2C-4E3B-8170-04C35918508C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAD8DCA-E941-4470-A793-6B74B34CB757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,25 +55,34 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT VEDL 31 Jul 2025 440 PE</t>
-  </si>
-  <si>
-    <t>09-07-2025</t>
-  </si>
-  <si>
-    <t>OPT GRANULES 31 Jul 2025 480 PE</t>
-  </si>
-  <si>
-    <t>10-07-2025</t>
-  </si>
-  <si>
-    <t>OPT PIIND 31 Jul 2025 4100 PE</t>
-  </si>
-  <si>
-    <t>OPT BHARTIARTL 31 Jul 2025 2000 PE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 10 Jul 2025 25400 PE</t>
+    <t>OPT POLYCAB 28 Aug 2025 6600 PE</t>
+  </si>
+  <si>
+    <t>12-08-2025</t>
+  </si>
+  <si>
+    <t>OPT JINDALSTEL 28 Aug 2025 1000 CE</t>
+  </si>
+  <si>
+    <t>13-08-2025</t>
+  </si>
+  <si>
+    <t>OPT BDL 28 Aug 2025 1500 CE</t>
+  </si>
+  <si>
+    <t>OPT IRCTC 28 Aug 2025 730 CE</t>
+  </si>
+  <si>
+    <t>14-08-2025</t>
+  </si>
+  <si>
+    <t>OPT KAYNES 28 Aug 2025 6100 CE</t>
+  </si>
+  <si>
+    <t>18-08-2025</t>
+  </si>
+  <si>
+    <t>OPT COFORGE 28 Aug 2025 1600 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -426,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -445,10 +454,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -457,10 +466,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -483,237 +492,284 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45847</v>
+        <v>45881</v>
       </c>
       <c r="D2">
-        <v>2300</v>
+        <v>125</v>
       </c>
       <c r="E2">
-        <v>20.329999999999998</v>
+        <v>135.25</v>
       </c>
       <c r="F2">
-        <v>46747.5</v>
+        <v>16906.25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>2300</v>
+        <v>125</v>
       </c>
       <c r="I2">
-        <v>22.25</v>
+        <v>118</v>
       </c>
       <c r="J2">
-        <v>51175</v>
+        <v>14750</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>4427.5</v>
+        <v>-2156.25</v>
       </c>
       <c r="M2">
-        <v>163.97</v>
+        <v>76.510000000000005</v>
       </c>
       <c r="N2">
-        <v>4263.53</v>
+        <v>-2232.7600000000002</v>
       </c>
       <c r="O2">
-        <v>4427.5</v>
+        <v>2156.25</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45848</v>
+        <v>45882</v>
       </c>
       <c r="D3">
-        <v>1075</v>
+        <v>625</v>
       </c>
       <c r="E3">
-        <v>20.350000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="F3">
-        <v>21876.25</v>
+        <v>19062.5</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H3">
-        <v>1075</v>
+        <v>625</v>
       </c>
       <c r="I3">
-        <v>20.3</v>
+        <v>27.5</v>
       </c>
       <c r="J3">
-        <v>21822.5</v>
+        <v>17187.5</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-53.75</v>
+        <v>-1875</v>
       </c>
       <c r="M3">
-        <v>88.39</v>
+        <v>80.2</v>
       </c>
       <c r="N3">
-        <v>-142.13999999999999</v>
+        <v>-1955.2</v>
       </c>
       <c r="O3">
-        <v>53.75</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>45848</v>
+        <v>45882</v>
       </c>
       <c r="D4">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="E4">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="F4">
-        <v>18550</v>
+        <v>22750</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H4">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="I4">
-        <v>108.4</v>
+        <v>81</v>
       </c>
       <c r="J4">
-        <v>18970</v>
+        <v>26325</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>420</v>
+        <v>3575</v>
       </c>
       <c r="M4">
-        <v>82.5</v>
+        <v>95.08</v>
       </c>
       <c r="N4">
-        <v>337.5</v>
+        <v>3479.92</v>
       </c>
       <c r="O4">
-        <v>420</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>45848</v>
+        <v>45883</v>
       </c>
       <c r="D5">
-        <v>475</v>
+        <v>875</v>
       </c>
       <c r="E5">
-        <v>43.85</v>
+        <v>11.95</v>
       </c>
       <c r="F5">
-        <v>20828.75</v>
+        <v>10456.25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H5">
-        <v>475</v>
+        <v>875</v>
       </c>
       <c r="I5">
-        <v>43.7</v>
+        <v>11.55</v>
       </c>
       <c r="J5">
-        <v>20757.5</v>
+        <v>10106.25</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-71.25</v>
+        <v>-350</v>
       </c>
       <c r="M5">
-        <v>86.06</v>
+        <v>66.27</v>
       </c>
       <c r="N5">
-        <v>-157.31</v>
+        <v>-416.27</v>
       </c>
       <c r="O5">
-        <v>71.25</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45883</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>210</v>
+      </c>
+      <c r="F6">
+        <v>21000</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>260</v>
+      </c>
+      <c r="J6">
+        <v>26000</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5000</v>
+      </c>
+      <c r="M6">
+        <v>93.6</v>
+      </c>
+      <c r="N6">
+        <v>4906.3999999999996</v>
+      </c>
+      <c r="O6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45883</v>
+      </c>
+      <c r="D7">
+        <v>375</v>
+      </c>
+      <c r="E7">
+        <v>62.3</v>
+      </c>
+      <c r="F7">
+        <v>23362.5</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1">
-        <v>45848</v>
-      </c>
-      <c r="D6">
-        <v>75</v>
-      </c>
-      <c r="E6">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="F6">
-        <v>2647.5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>75</v>
-      </c>
-      <c r="I6">
-        <v>29.25</v>
-      </c>
-      <c r="J6">
-        <v>2193.75</v>
-      </c>
-      <c r="K6">
+      <c r="H7">
+        <v>375</v>
+      </c>
+      <c r="I7">
+        <v>56</v>
+      </c>
+      <c r="J7">
+        <v>21000</v>
+      </c>
+      <c r="K7">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>-453.75</v>
-      </c>
-      <c r="M6">
-        <v>51.51</v>
-      </c>
-      <c r="N6">
-        <v>-505.26</v>
-      </c>
-      <c r="O6">
-        <v>453.75</v>
+      <c r="L7">
+        <v>-2362.5</v>
+      </c>
+      <c r="M7">
+        <v>87.81</v>
+      </c>
+      <c r="N7">
+        <v>-2450.31</v>
+      </c>
+      <c r="O7">
+        <v>2362.5</v>
       </c>
     </row>
   </sheetData>
